--- a/AAII_Financials/Quarterly/BNPQY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BNPQY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="92">
   <si>
     <t>BNPQY</t>
   </si>
@@ -656,74 +656,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -769,8 +772,11 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,8 +822,11 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +872,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -882,8 +894,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -929,8 +942,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -976,8 +992,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1023,8 +1042,11 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1070,8 +1092,11 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1086,8 +1111,9 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1133,8 +1159,11 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1180,8 +1209,11 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1199,8 +1231,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1246,8 +1279,11 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1293,8 +1329,11 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1340,8 +1379,11 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1387,8 +1429,11 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1434,8 +1479,11 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1481,8 +1529,11 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1528,8 +1579,11 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1575,8 +1629,11 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1622,8 +1679,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1669,8 +1729,11 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1716,8 +1779,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1763,8 +1829,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1810,8 +1879,11 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1857,8 +1929,11 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1904,8 +1979,11 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1951,60 +2029,66 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2022,8 +2106,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2041,149 +2126,159 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>258321700</v>
+      </c>
+      <c r="E41" s="3">
         <v>217567200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>260406200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>230280400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>246002300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>215275600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>198755600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>208513300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>210735000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>215341500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>327855600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>285647800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>330512000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>365195600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>353197600</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1143154300</v>
+      </c>
+      <c r="E42" s="3">
         <v>1100500400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1007661100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1060437600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1089554900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>969649800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>856709800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1002723600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>956177000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>970746600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>994209100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>945515500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>918009800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>884046100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>898391600</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>58821000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6649400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>55334000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6488300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>57103900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5955500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>47362000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7540700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>55992700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6998600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>53432100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5836200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>50122300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6057100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>50261800</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2229,243 +2324,261 @@
       <c r="Q44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>190401000</v>
+      </c>
+      <c r="E45" s="3">
         <v>230947800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>153127900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>198991000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>145395200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>186587800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>135392900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>199860600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>133886200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>183303500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>137710800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>184635900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>136369000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200111900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>266917800</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1650698000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1555664700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1476529300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1496197300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1538056400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1377468700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1238220300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1418638200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1356791000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1376390100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1513207700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1421635300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1435013100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1455410700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1568768800</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>674011200</v>
+      </c>
+      <c r="E47" s="3">
         <v>645468700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>642079400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>640124400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>634576600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>572944200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>533758200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>544663200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>506839200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>494888300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>309898300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>435575800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>454402800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>448327900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>275071100</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>62417500</v>
+      </c>
+      <c r="E48" s="3">
         <v>62333700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>62486800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>61481900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>60432200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>55157800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>51547800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>54517100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>51296500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>50240600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>49448400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>45680600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>45636500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>43298600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>40546100</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>13596500</v>
+      </c>
+      <c r="E49" s="3">
         <v>13599700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>13756000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13495200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11483300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10701500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10293000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11059600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10680400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10416400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10711800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10115400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10421400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9939200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9708200</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2511,8 +2624,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2558,55 +2674,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3">
+        <v>8919200</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3">
         <v>9908400</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3">
         <v>9266000</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3">
         <v>9241100</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L52" s="3">
         <v>9486800</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N52" s="3">
         <v>10401200</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P52" s="3">
         <v>9950900</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q52" s="3">
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R52" s="3">
         <v>10987500</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2652,55 +2774,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3523156600</v>
+      </c>
+      <c r="E54" s="3">
         <v>3380063400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3279301400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3314060800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3346301800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3028581900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2800401700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3070584400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2892165400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2912980900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2864484400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2859189200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2916136500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2926766600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2846797100</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2718,8 +2846,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2737,290 +2866,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1293345100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1358579500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1237553100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1348939300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1219011200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1223516000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1083811000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1227018700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1090758600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1160353900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1108065700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1156403500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1085468300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1262448900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1094980200</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>537820200</v>
+      </c>
+      <c r="E58" s="3">
         <v>354883000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>442680500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>320857700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>516319400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>291054900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>452548900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>329153500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>447114500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>316259600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>453885300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>353159400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>493700900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>298277900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>415070000</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>583603300</v>
+      </c>
+      <c r="E59" s="3">
         <v>575037500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>544953600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>574419800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>585572500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>536542400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>401440100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>539848300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>488166700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>513001400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>422510200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>485294200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>474787100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>488084500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>441869200</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2425243900</v>
+      </c>
+      <c r="E60" s="3">
         <v>2485450200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2235337600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2410797800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2330122100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2205374000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1946598000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2259973200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2035460200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2150025900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1993596800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2160611800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2062367900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2230013000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1963513900</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>411620000</v>
+      </c>
+      <c r="E61" s="3">
         <v>398654400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>394810400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>410840100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>372003500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>374545000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>301744500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>373905900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>305429100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>350968800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>314199200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>310333400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>300708500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>290474800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>316009400</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>518669000</v>
+      </c>
+      <c r="E62" s="3">
         <v>338295900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>488619200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>339897900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>480777500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>301373800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>408644800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>290900100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>406529500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>271037900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>409414200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>251377000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>405208500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>262856400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>428137200</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3066,8 +3214,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3113,8 +3264,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3160,55 +3314,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3364986900</v>
+      </c>
+      <c r="E66" s="3">
         <v>3222400600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3124114100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3161535800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3191704100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2881292700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2661525000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2924779200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2755267300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2772032600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2722042700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2722322200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2776066600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2783344200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2712127800</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3226,8 +3386,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3273,8 +3434,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3320,8 +3484,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3367,8 +3534,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3414,55 +3584,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="D72" s="3">
+        <v>121987900</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="3">
         <v>104902000</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3">
         <v>109049900</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3">
         <v>89755700</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>93048300</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>89681700</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3">
         <v>97197600</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R72" s="3">
         <v>92835300</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3508,8 +3684,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3555,8 +3734,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3602,55 +3784,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>150716300</v>
+      </c>
+      <c r="E76" s="3">
         <v>149866300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>147367600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>145306800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>147605400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>140634500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>132660700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>139372100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>130914000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>134870000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>136776800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>131390800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>134608100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>138141000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>129568200</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3696,60 +3884,66 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3795,8 +3989,11 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3814,8 +4011,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3861,8 +4059,11 @@
       <c r="Q83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3908,8 +4109,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3955,8 +4159,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4002,8 +4209,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4049,8 +4259,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4096,8 +4309,11 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4143,8 +4359,11 @@
       <c r="Q89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4162,8 +4381,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4209,8 +4429,11 @@
       <c r="Q91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4256,8 +4479,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4303,8 +4529,11 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4350,8 +4579,11 @@
       <c r="Q94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4369,8 +4601,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4416,8 +4649,11 @@
       <c r="Q96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4463,8 +4699,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4510,8 +4749,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4557,8 +4799,11 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4604,8 +4849,11 @@
       <c r="Q100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4651,8 +4899,11 @@
       <c r="Q101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4696,6 +4947,9 @@
         <v>4</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
